--- a/discharge_forms/014_pediatric_discharge_form--discharge_forms.xlsx
+++ b/discharge_forms/014_pediatric_discharge_form--discharge_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'acute_lymphatic_leukemia_(all)'}</t>
+          <t>acute_lymphatic_leukemia_(all)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Acute lymphatic leukemia (ALL)'}</t>
+          <t>Acute lymphatic leukemia (ALL)</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'bronchitis'}</t>
+          <t>bronchitis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Bronchitis'}</t>
+          <t>Bronchitis</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'congenital_heart_disease'}</t>
+          <t>congenital_heart_disease</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Congenital heart disease'}</t>
+          <t>Congenital heart disease</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'cough'}</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Cough'}</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'diarrhea'}</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Diarrhea'}</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'fever'}</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Fever'}</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'fever_with_vomiting'}</t>
+          <t>fever_with_vomiting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Fever with vomiting'}</t>
+          <t>Fever with vomiting</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'pneumonia'}</t>
+          <t>pneumonia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Pneumonia'}</t>
+          <t>Pneumonia</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'respiratory_syncytial_virus_(rsv)_infection'}</t>
+          <t>respiratory_syncytial_virus_(rsv)_infection</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Respiratory syncytial virus (RSV) infection'}</t>
+          <t>Respiratory syncytial virus (RSV) infection</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'vomiting'}</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Vomiting'}</t>
+          <t>Vomiting</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'primary_care_physician'}</t>
+          <t>primary_care_physician</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Primary Care Physician'}</t>
+          <t>Primary Care Physician</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'pediatrician'}</t>
+          <t>pediatrician</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Pediatrician'}</t>
+          <t>Pediatrician</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'cardiologist'}</t>
+          <t>cardiologist</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Cardiologist'}</t>
+          <t>Cardiologist</t>
         </is>
       </c>
     </row>
